--- a/synuclein_inclusion_biogenesis_2024/image_analysis/mitophagy/72425_SUMMARY.xlsx
+++ b/synuclein_inclusion_biogenesis_2024/image_analysis/mitophagy/72425_SUMMARY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B145"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,11 @@
           <t>Cell Number</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Number of Inclusions</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -449,6 +454,9 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -459,6 +467,9 @@
       <c r="B3" t="n">
         <v>2</v>
       </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -469,6 +480,9 @@
       <c r="B4" t="n">
         <v>3</v>
       </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -479,6 +493,9 @@
       <c r="B5" t="n">
         <v>4</v>
       </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -489,6 +506,9 @@
       <c r="B6" t="n">
         <v>5</v>
       </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -499,6 +519,9 @@
       <c r="B7" t="n">
         <v>6</v>
       </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -509,6 +532,9 @@
       <c r="B8" t="n">
         <v>7</v>
       </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -519,6 +545,9 @@
       <c r="B9" t="n">
         <v>8</v>
       </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -529,6 +558,9 @@
       <c r="B10" t="n">
         <v>9</v>
       </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -539,6 +571,9 @@
       <c r="B11" t="n">
         <v>10</v>
       </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -549,6 +584,9 @@
       <c r="B12" t="n">
         <v>11</v>
       </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -559,6 +597,9 @@
       <c r="B13" t="n">
         <v>1</v>
       </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -569,6 +610,9 @@
       <c r="B14" t="n">
         <v>2</v>
       </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -579,6 +623,9 @@
       <c r="B15" t="n">
         <v>3</v>
       </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -589,6 +636,9 @@
       <c r="B16" t="n">
         <v>4</v>
       </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -599,6 +649,9 @@
       <c r="B17" t="n">
         <v>5</v>
       </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -609,6 +662,9 @@
       <c r="B18" t="n">
         <v>6</v>
       </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -619,6 +675,9 @@
       <c r="B19" t="n">
         <v>7</v>
       </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -629,6 +688,9 @@
       <c r="B20" t="n">
         <v>8</v>
       </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -639,6 +701,9 @@
       <c r="B21" t="n">
         <v>9</v>
       </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -649,6 +714,9 @@
       <c r="B22" t="n">
         <v>1</v>
       </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -659,6 +727,9 @@
       <c r="B23" t="n">
         <v>2</v>
       </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -669,6 +740,9 @@
       <c r="B24" t="n">
         <v>3</v>
       </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -679,6 +753,9 @@
       <c r="B25" t="n">
         <v>4</v>
       </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -689,6 +766,9 @@
       <c r="B26" t="n">
         <v>5</v>
       </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -699,6 +779,9 @@
       <c r="B27" t="n">
         <v>6</v>
       </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -709,6 +792,9 @@
       <c r="B28" t="n">
         <v>7</v>
       </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -719,6 +805,9 @@
       <c r="B29" t="n">
         <v>1</v>
       </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -729,6 +818,9 @@
       <c r="B30" t="n">
         <v>2</v>
       </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -739,6 +831,9 @@
       <c r="B31" t="n">
         <v>3</v>
       </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -749,6 +844,9 @@
       <c r="B32" t="n">
         <v>1</v>
       </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -759,6 +857,9 @@
       <c r="B33" t="n">
         <v>2</v>
       </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -769,6 +870,9 @@
       <c r="B34" t="n">
         <v>3</v>
       </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -779,6 +883,9 @@
       <c r="B35" t="n">
         <v>4</v>
       </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -789,6 +896,9 @@
       <c r="B36" t="n">
         <v>1</v>
       </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -799,6 +909,9 @@
       <c r="B37" t="n">
         <v>2</v>
       </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -809,6 +922,9 @@
       <c r="B38" t="n">
         <v>3</v>
       </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -819,6 +935,9 @@
       <c r="B39" t="n">
         <v>4</v>
       </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -829,6 +948,9 @@
       <c r="B40" t="n">
         <v>5</v>
       </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -839,6 +961,9 @@
       <c r="B41" t="n">
         <v>6</v>
       </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -849,6 +974,9 @@
       <c r="B42" t="n">
         <v>1</v>
       </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -859,6 +987,9 @@
       <c r="B43" t="n">
         <v>2</v>
       </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -869,6 +1000,9 @@
       <c r="B44" t="n">
         <v>3</v>
       </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -879,6 +1013,9 @@
       <c r="B45" t="n">
         <v>4</v>
       </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -889,6 +1026,9 @@
       <c r="B46" t="n">
         <v>5</v>
       </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -899,6 +1039,9 @@
       <c r="B47" t="n">
         <v>1</v>
       </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -909,6 +1052,9 @@
       <c r="B48" t="n">
         <v>2</v>
       </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -919,6 +1065,9 @@
       <c r="B49" t="n">
         <v>3</v>
       </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -929,6 +1078,9 @@
       <c r="B50" t="n">
         <v>4</v>
       </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -939,6 +1091,9 @@
       <c r="B51" t="n">
         <v>5</v>
       </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -949,6 +1104,9 @@
       <c r="B52" t="n">
         <v>6</v>
       </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -959,6 +1117,9 @@
       <c r="B53" t="n">
         <v>1</v>
       </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -969,6 +1130,9 @@
       <c r="B54" t="n">
         <v>2</v>
       </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -979,6 +1143,9 @@
       <c r="B55" t="n">
         <v>3</v>
       </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -989,6 +1156,9 @@
       <c r="B56" t="n">
         <v>4</v>
       </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -999,6 +1169,9 @@
       <c r="B57" t="n">
         <v>1</v>
       </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1009,6 +1182,9 @@
       <c r="B58" t="n">
         <v>2</v>
       </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1019,6 +1195,9 @@
       <c r="B59" t="n">
         <v>3</v>
       </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1029,6 +1208,9 @@
       <c r="B60" t="n">
         <v>4</v>
       </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1039,6 +1221,9 @@
       <c r="B61" t="n">
         <v>5</v>
       </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1049,6 +1234,9 @@
       <c r="B62" t="n">
         <v>6</v>
       </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1059,6 +1247,9 @@
       <c r="B63" t="n">
         <v>1</v>
       </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1069,6 +1260,9 @@
       <c r="B64" t="n">
         <v>2</v>
       </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1079,6 +1273,9 @@
       <c r="B65" t="n">
         <v>3</v>
       </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1089,6 +1286,9 @@
       <c r="B66" t="n">
         <v>1</v>
       </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1099,6 +1299,9 @@
       <c r="B67" t="n">
         <v>2</v>
       </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1109,6 +1312,9 @@
       <c r="B68" t="n">
         <v>3</v>
       </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1119,6 +1325,9 @@
       <c r="B69" t="n">
         <v>4</v>
       </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1129,6 +1338,9 @@
       <c r="B70" t="n">
         <v>5</v>
       </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1139,6 +1351,9 @@
       <c r="B71" t="n">
         <v>6</v>
       </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1149,6 +1364,9 @@
       <c r="B72" t="n">
         <v>7</v>
       </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1159,6 +1377,9 @@
       <c r="B73" t="n">
         <v>8</v>
       </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1169,6 +1390,9 @@
       <c r="B74" t="n">
         <v>9</v>
       </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1179,6 +1403,9 @@
       <c r="B75" t="n">
         <v>10</v>
       </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1189,6 +1416,9 @@
       <c r="B76" t="n">
         <v>1</v>
       </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1199,6 +1429,9 @@
       <c r="B77" t="n">
         <v>2</v>
       </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1209,6 +1442,9 @@
       <c r="B78" t="n">
         <v>3</v>
       </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1219,6 +1455,9 @@
       <c r="B79" t="n">
         <v>4</v>
       </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1229,6 +1468,9 @@
       <c r="B80" t="n">
         <v>5</v>
       </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1239,6 +1481,9 @@
       <c r="B81" t="n">
         <v>1</v>
       </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1249,6 +1494,9 @@
       <c r="B82" t="n">
         <v>2</v>
       </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1259,6 +1507,9 @@
       <c r="B83" t="n">
         <v>3</v>
       </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1269,6 +1520,9 @@
       <c r="B84" t="n">
         <v>4</v>
       </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1279,6 +1533,9 @@
       <c r="B85" t="n">
         <v>1</v>
       </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1289,6 +1546,9 @@
       <c r="B86" t="n">
         <v>2</v>
       </c>
+      <c r="C86" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1299,6 +1559,9 @@
       <c r="B87" t="n">
         <v>1</v>
       </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1309,6 +1572,9 @@
       <c r="B88" t="n">
         <v>2</v>
       </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1319,6 +1585,9 @@
       <c r="B89" t="n">
         <v>3</v>
       </c>
+      <c r="C89" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1329,6 +1598,9 @@
       <c r="B90" t="n">
         <v>4</v>
       </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1339,6 +1611,9 @@
       <c r="B91" t="n">
         <v>5</v>
       </c>
+      <c r="C91" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1349,6 +1624,9 @@
       <c r="B92" t="n">
         <v>6</v>
       </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1359,6 +1637,9 @@
       <c r="B93" t="n">
         <v>1</v>
       </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1369,6 +1650,9 @@
       <c r="B94" t="n">
         <v>2</v>
       </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1379,6 +1663,9 @@
       <c r="B95" t="n">
         <v>3</v>
       </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1389,6 +1676,9 @@
       <c r="B96" t="n">
         <v>4</v>
       </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1399,6 +1689,9 @@
       <c r="B97" t="n">
         <v>5</v>
       </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1409,6 +1702,9 @@
       <c r="B98" t="n">
         <v>6</v>
       </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1419,6 +1715,9 @@
       <c r="B99" t="n">
         <v>7</v>
       </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1429,6 +1728,9 @@
       <c r="B100" t="n">
         <v>8</v>
       </c>
+      <c r="C100" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1439,6 +1741,9 @@
       <c r="B101" t="n">
         <v>9</v>
       </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1449,6 +1754,9 @@
       <c r="B102" t="n">
         <v>1</v>
       </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1459,6 +1767,9 @@
       <c r="B103" t="n">
         <v>2</v>
       </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1469,6 +1780,9 @@
       <c r="B104" t="n">
         <v>3</v>
       </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1479,6 +1793,9 @@
       <c r="B105" t="n">
         <v>4</v>
       </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1489,6 +1806,9 @@
       <c r="B106" t="n">
         <v>5</v>
       </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1499,6 +1819,9 @@
       <c r="B107" t="n">
         <v>1</v>
       </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1509,6 +1832,9 @@
       <c r="B108" t="n">
         <v>2</v>
       </c>
+      <c r="C108" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1519,6 +1845,9 @@
       <c r="B109" t="n">
         <v>1</v>
       </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1529,6 +1858,9 @@
       <c r="B110" t="n">
         <v>2</v>
       </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1539,6 +1871,9 @@
       <c r="B111" t="n">
         <v>3</v>
       </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1549,6 +1884,9 @@
       <c r="B112" t="n">
         <v>4</v>
       </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1559,6 +1897,9 @@
       <c r="B113" t="n">
         <v>5</v>
       </c>
+      <c r="C113" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1569,6 +1910,9 @@
       <c r="B114" t="n">
         <v>6</v>
       </c>
+      <c r="C114" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1579,6 +1923,9 @@
       <c r="B115" t="n">
         <v>1</v>
       </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1589,6 +1936,9 @@
       <c r="B116" t="n">
         <v>2</v>
       </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1599,6 +1949,9 @@
       <c r="B117" t="n">
         <v>3</v>
       </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1609,6 +1962,9 @@
       <c r="B118" t="n">
         <v>4</v>
       </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1619,6 +1975,9 @@
       <c r="B119" t="n">
         <v>1</v>
       </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1629,6 +1988,9 @@
       <c r="B120" t="n">
         <v>2</v>
       </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1639,6 +2001,9 @@
       <c r="B121" t="n">
         <v>3</v>
       </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1649,6 +2014,9 @@
       <c r="B122" t="n">
         <v>4</v>
       </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1659,6 +2027,9 @@
       <c r="B123" t="n">
         <v>5</v>
       </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1669,6 +2040,9 @@
       <c r="B124" t="n">
         <v>6</v>
       </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1679,6 +2053,9 @@
       <c r="B125" t="n">
         <v>7</v>
       </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1689,6 +2066,9 @@
       <c r="B126" t="n">
         <v>8</v>
       </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1699,6 +2079,9 @@
       <c r="B127" t="n">
         <v>1</v>
       </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1709,6 +2092,9 @@
       <c r="B128" t="n">
         <v>2</v>
       </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1719,6 +2105,9 @@
       <c r="B129" t="n">
         <v>3</v>
       </c>
+      <c r="C129" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1729,6 +2118,9 @@
       <c r="B130" t="n">
         <v>4</v>
       </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1739,6 +2131,9 @@
       <c r="B131" t="n">
         <v>5</v>
       </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1749,6 +2144,9 @@
       <c r="B132" t="n">
         <v>1</v>
       </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1759,6 +2157,9 @@
       <c r="B133" t="n">
         <v>2</v>
       </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1769,6 +2170,9 @@
       <c r="B134" t="n">
         <v>3</v>
       </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1779,6 +2183,9 @@
       <c r="B135" t="n">
         <v>4</v>
       </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1789,6 +2196,9 @@
       <c r="B136" t="n">
         <v>1</v>
       </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1799,6 +2209,9 @@
       <c r="B137" t="n">
         <v>2</v>
       </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1809,6 +2222,9 @@
       <c r="B138" t="n">
         <v>3</v>
       </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1819,6 +2235,9 @@
       <c r="B139" t="n">
         <v>4</v>
       </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1829,6 +2248,9 @@
       <c r="B140" t="n">
         <v>5</v>
       </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1839,6 +2261,9 @@
       <c r="B141" t="n">
         <v>6</v>
       </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1849,6 +2274,9 @@
       <c r="B142" t="n">
         <v>7</v>
       </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1859,6 +2287,9 @@
       <c r="B143" t="n">
         <v>8</v>
       </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1869,6 +2300,9 @@
       <c r="B144" t="n">
         <v>9</v>
       </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1878,6 +2312,9 @@
       </c>
       <c r="B145" t="n">
         <v>10</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/synuclein_inclusion_biogenesis_2024/image_analysis/mitophagy/72425_SUMMARY.xlsx
+++ b/synuclein_inclusion_biogenesis_2024/image_analysis/mitophagy/72425_SUMMARY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,16 @@
           <t>Number of Inclusions</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Number of Mitophagy Events in Donut</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Number of Mitophagy Events Outside Dialated Area</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -457,6 +467,12 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -470,6 +486,12 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -483,6 +505,12 @@
       <c r="C4" t="n">
         <v>1</v>
       </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -496,6 +524,12 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -509,6 +543,12 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -522,6 +562,12 @@
       <c r="C7" t="n">
         <v>1</v>
       </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -535,6 +581,12 @@
       <c r="C8" t="n">
         <v>0</v>
       </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -548,6 +600,12 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -561,6 +619,12 @@
       <c r="C10" t="n">
         <v>0</v>
       </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -574,6 +638,12 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -587,6 +657,12 @@
       <c r="C12" t="n">
         <v>0</v>
       </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -600,6 +676,12 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -613,6 +695,12 @@
       <c r="C14" t="n">
         <v>0</v>
       </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -626,6 +714,12 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -639,6 +733,12 @@
       <c r="C16" t="n">
         <v>0</v>
       </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -652,6 +752,12 @@
       <c r="C17" t="n">
         <v>1</v>
       </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -665,6 +771,12 @@
       <c r="C18" t="n">
         <v>0</v>
       </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -678,6 +790,12 @@
       <c r="C19" t="n">
         <v>0</v>
       </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -691,6 +809,12 @@
       <c r="C20" t="n">
         <v>0</v>
       </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -704,6 +828,12 @@
       <c r="C21" t="n">
         <v>0</v>
       </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -717,6 +847,12 @@
       <c r="C22" t="n">
         <v>0</v>
       </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -730,6 +866,12 @@
       <c r="C23" t="n">
         <v>0</v>
       </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -743,6 +885,12 @@
       <c r="C24" t="n">
         <v>0</v>
       </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -756,6 +904,12 @@
       <c r="C25" t="n">
         <v>2</v>
       </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -769,6 +923,12 @@
       <c r="C26" t="n">
         <v>0</v>
       </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -782,6 +942,12 @@
       <c r="C27" t="n">
         <v>0</v>
       </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -795,6 +961,12 @@
       <c r="C28" t="n">
         <v>0</v>
       </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -808,6 +980,12 @@
       <c r="C29" t="n">
         <v>0</v>
       </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -821,6 +999,12 @@
       <c r="C30" t="n">
         <v>1</v>
       </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -834,6 +1018,12 @@
       <c r="C31" t="n">
         <v>0</v>
       </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -847,6 +1037,12 @@
       <c r="C32" t="n">
         <v>3</v>
       </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -860,6 +1056,12 @@
       <c r="C33" t="n">
         <v>0</v>
       </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -873,6 +1075,12 @@
       <c r="C34" t="n">
         <v>2</v>
       </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -886,6 +1094,12 @@
       <c r="C35" t="n">
         <v>0</v>
       </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -899,6 +1113,12 @@
       <c r="C36" t="n">
         <v>0</v>
       </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -912,6 +1132,12 @@
       <c r="C37" t="n">
         <v>0</v>
       </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -925,6 +1151,12 @@
       <c r="C38" t="n">
         <v>0</v>
       </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -938,6 +1170,12 @@
       <c r="C39" t="n">
         <v>0</v>
       </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -951,6 +1189,12 @@
       <c r="C40" t="n">
         <v>2</v>
       </c>
+      <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -964,6 +1208,12 @@
       <c r="C41" t="n">
         <v>0</v>
       </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -977,6 +1227,12 @@
       <c r="C42" t="n">
         <v>0</v>
       </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -990,6 +1246,12 @@
       <c r="C43" t="n">
         <v>1</v>
       </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1003,6 +1265,12 @@
       <c r="C44" t="n">
         <v>0</v>
       </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1016,6 +1284,12 @@
       <c r="C45" t="n">
         <v>3</v>
       </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1029,6 +1303,12 @@
       <c r="C46" t="n">
         <v>0</v>
       </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1042,6 +1322,12 @@
       <c r="C47" t="n">
         <v>1</v>
       </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1055,6 +1341,12 @@
       <c r="C48" t="n">
         <v>0</v>
       </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1068,6 +1360,12 @@
       <c r="C49" t="n">
         <v>0</v>
       </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1081,6 +1379,12 @@
       <c r="C50" t="n">
         <v>0</v>
       </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1094,6 +1398,12 @@
       <c r="C51" t="n">
         <v>0</v>
       </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1107,6 +1417,12 @@
       <c r="C52" t="n">
         <v>0</v>
       </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1120,6 +1436,12 @@
       <c r="C53" t="n">
         <v>0</v>
       </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1133,6 +1455,12 @@
       <c r="C54" t="n">
         <v>1</v>
       </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1146,6 +1474,12 @@
       <c r="C55" t="n">
         <v>0</v>
       </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1159,6 +1493,12 @@
       <c r="C56" t="n">
         <v>1</v>
       </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1172,6 +1512,12 @@
       <c r="C57" t="n">
         <v>0</v>
       </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1185,6 +1531,12 @@
       <c r="C58" t="n">
         <v>1</v>
       </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1198,6 +1550,12 @@
       <c r="C59" t="n">
         <v>1</v>
       </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1211,6 +1569,12 @@
       <c r="C60" t="n">
         <v>0</v>
       </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1224,6 +1588,12 @@
       <c r="C61" t="n">
         <v>0</v>
       </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1237,6 +1607,12 @@
       <c r="C62" t="n">
         <v>0</v>
       </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1250,6 +1626,12 @@
       <c r="C63" t="n">
         <v>0</v>
       </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1263,6 +1645,12 @@
       <c r="C64" t="n">
         <v>0</v>
       </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1276,6 +1664,12 @@
       <c r="C65" t="n">
         <v>2</v>
       </c>
+      <c r="D65" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1289,6 +1683,12 @@
       <c r="C66" t="n">
         <v>2</v>
       </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1302,6 +1702,12 @@
       <c r="C67" t="n">
         <v>0</v>
       </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1315,6 +1721,12 @@
       <c r="C68" t="n">
         <v>0</v>
       </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1328,6 +1740,12 @@
       <c r="C69" t="n">
         <v>0</v>
       </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1341,6 +1759,12 @@
       <c r="C70" t="n">
         <v>1</v>
       </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1354,6 +1778,12 @@
       <c r="C71" t="n">
         <v>0</v>
       </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1367,6 +1797,12 @@
       <c r="C72" t="n">
         <v>0</v>
       </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1380,6 +1816,12 @@
       <c r="C73" t="n">
         <v>2</v>
       </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1393,6 +1835,12 @@
       <c r="C74" t="n">
         <v>0</v>
       </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1406,6 +1854,12 @@
       <c r="C75" t="n">
         <v>0</v>
       </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1419,6 +1873,12 @@
       <c r="C76" t="n">
         <v>1</v>
       </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1432,6 +1892,12 @@
       <c r="C77" t="n">
         <v>1</v>
       </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1445,6 +1911,12 @@
       <c r="C78" t="n">
         <v>1</v>
       </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1458,6 +1930,12 @@
       <c r="C79" t="n">
         <v>0</v>
       </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1471,6 +1949,12 @@
       <c r="C80" t="n">
         <v>1</v>
       </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1484,6 +1968,12 @@
       <c r="C81" t="n">
         <v>0</v>
       </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1497,6 +1987,12 @@
       <c r="C82" t="n">
         <v>1</v>
       </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1510,6 +2006,12 @@
       <c r="C83" t="n">
         <v>2</v>
       </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1523,6 +2025,12 @@
       <c r="C84" t="n">
         <v>0</v>
       </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1536,6 +2044,12 @@
       <c r="C85" t="n">
         <v>0</v>
       </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1549,6 +2063,12 @@
       <c r="C86" t="n">
         <v>3</v>
       </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1562,6 +2082,12 @@
       <c r="C87" t="n">
         <v>0</v>
       </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1575,6 +2101,12 @@
       <c r="C88" t="n">
         <v>0</v>
       </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1588,6 +2120,12 @@
       <c r="C89" t="n">
         <v>2</v>
       </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1601,6 +2139,12 @@
       <c r="C90" t="n">
         <v>2</v>
       </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1614,6 +2158,12 @@
       <c r="C91" t="n">
         <v>4</v>
       </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1627,6 +2177,12 @@
       <c r="C92" t="n">
         <v>1</v>
       </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1640,6 +2196,12 @@
       <c r="C93" t="n">
         <v>0</v>
       </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1653,6 +2215,12 @@
       <c r="C94" t="n">
         <v>0</v>
       </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1666,6 +2234,12 @@
       <c r="C95" t="n">
         <v>1</v>
       </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1679,6 +2253,12 @@
       <c r="C96" t="n">
         <v>0</v>
       </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1692,6 +2272,12 @@
       <c r="C97" t="n">
         <v>0</v>
       </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1705,6 +2291,12 @@
       <c r="C98" t="n">
         <v>0</v>
       </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1718,6 +2310,12 @@
       <c r="C99" t="n">
         <v>1</v>
       </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1731,6 +2329,12 @@
       <c r="C100" t="n">
         <v>2</v>
       </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1744,6 +2348,12 @@
       <c r="C101" t="n">
         <v>0</v>
       </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1757,6 +2367,12 @@
       <c r="C102" t="n">
         <v>0</v>
       </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1770,6 +2386,12 @@
       <c r="C103" t="n">
         <v>2</v>
       </c>
+      <c r="D103" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1783,6 +2405,12 @@
       <c r="C104" t="n">
         <v>1</v>
       </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1796,6 +2424,12 @@
       <c r="C105" t="n">
         <v>0</v>
       </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1809,6 +2443,12 @@
       <c r="C106" t="n">
         <v>0</v>
       </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1822,6 +2462,12 @@
       <c r="C107" t="n">
         <v>0</v>
       </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1835,6 +2481,12 @@
       <c r="C108" t="n">
         <v>6</v>
       </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1848,6 +2500,12 @@
       <c r="C109" t="n">
         <v>0</v>
       </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1861,6 +2519,12 @@
       <c r="C110" t="n">
         <v>0</v>
       </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1874,6 +2538,12 @@
       <c r="C111" t="n">
         <v>0</v>
       </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1887,6 +2557,12 @@
       <c r="C112" t="n">
         <v>0</v>
       </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1900,6 +2576,12 @@
       <c r="C113" t="n">
         <v>3</v>
       </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1913,6 +2595,12 @@
       <c r="C114" t="n">
         <v>3</v>
       </c>
+      <c r="D114" t="n">
+        <v>4</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1926,6 +2614,12 @@
       <c r="C115" t="n">
         <v>0</v>
       </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1939,6 +2633,12 @@
       <c r="C116" t="n">
         <v>0</v>
       </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1952,6 +2652,12 @@
       <c r="C117" t="n">
         <v>1</v>
       </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1965,6 +2671,12 @@
       <c r="C118" t="n">
         <v>1</v>
       </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1978,6 +2690,12 @@
       <c r="C119" t="n">
         <v>0</v>
       </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1991,6 +2709,12 @@
       <c r="C120" t="n">
         <v>0</v>
       </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2004,6 +2728,12 @@
       <c r="C121" t="n">
         <v>0</v>
       </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2017,6 +2747,12 @@
       <c r="C122" t="n">
         <v>1</v>
       </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2030,6 +2766,12 @@
       <c r="C123" t="n">
         <v>0</v>
       </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2043,6 +2785,12 @@
       <c r="C124" t="n">
         <v>0</v>
       </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2056,6 +2804,12 @@
       <c r="C125" t="n">
         <v>0</v>
       </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2069,6 +2823,12 @@
       <c r="C126" t="n">
         <v>0</v>
       </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2082,6 +2842,12 @@
       <c r="C127" t="n">
         <v>0</v>
       </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2095,6 +2861,12 @@
       <c r="C128" t="n">
         <v>0</v>
       </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2108,6 +2880,12 @@
       <c r="C129" t="n">
         <v>2</v>
       </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2121,6 +2899,12 @@
       <c r="C130" t="n">
         <v>1</v>
       </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2134,6 +2918,12 @@
       <c r="C131" t="n">
         <v>0</v>
       </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2147,6 +2937,12 @@
       <c r="C132" t="n">
         <v>1</v>
       </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2160,6 +2956,12 @@
       <c r="C133" t="n">
         <v>0</v>
       </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2173,6 +2975,12 @@
       <c r="C134" t="n">
         <v>0</v>
       </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2186,6 +2994,12 @@
       <c r="C135" t="n">
         <v>0</v>
       </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2199,6 +3013,12 @@
       <c r="C136" t="n">
         <v>0</v>
       </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2212,6 +3032,12 @@
       <c r="C137" t="n">
         <v>0</v>
       </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2225,6 +3051,12 @@
       <c r="C138" t="n">
         <v>0</v>
       </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2238,6 +3070,12 @@
       <c r="C139" t="n">
         <v>0</v>
       </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2251,6 +3089,12 @@
       <c r="C140" t="n">
         <v>1</v>
       </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2264,6 +3108,12 @@
       <c r="C141" t="n">
         <v>0</v>
       </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2277,6 +3127,12 @@
       <c r="C142" t="n">
         <v>0</v>
       </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2290,6 +3146,12 @@
       <c r="C143" t="n">
         <v>0</v>
       </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2303,6 +3165,12 @@
       <c r="C144" t="n">
         <v>0</v>
       </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2314,6 +3182,12 @@
         <v>10</v>
       </c>
       <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
         <v>0</v>
       </c>
     </row>

--- a/synuclein_inclusion_biogenesis_2024/image_analysis/mitophagy/72425_SUMMARY.xlsx
+++ b/synuclein_inclusion_biogenesis_2024/image_analysis/mitophagy/72425_SUMMARY.xlsx
@@ -566,7 +566,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -756,7 +756,7 @@
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1193,7 +1193,7 @@
         <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -1326,7 +1326,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -1459,7 +1459,7 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -1668,7 +1668,7 @@
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
@@ -1991,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -2067,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
@@ -2314,7 +2314,7 @@
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -2390,7 +2390,7 @@
         <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
@@ -2599,7 +2599,7 @@
         <v>4</v>
       </c>
       <c r="E114" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
@@ -2751,7 +2751,7 @@
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -2903,7 +2903,7 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">

--- a/synuclein_inclusion_biogenesis_2024/image_analysis/mitophagy/72425_SUMMARY.xlsx
+++ b/synuclein_inclusion_biogenesis_2024/image_analysis/mitophagy/72425_SUMMARY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E145"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,16 @@
           <t>Number of Mitophagy Events Outside Dialated Area</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Surface Area of Donut</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Surface Area of Cytoplasm without Donut</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -473,6 +483,12 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15499</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -492,6 +508,12 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>18113</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -511,6 +533,12 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
+      <c r="F4" t="n">
+        <v>1465</v>
+      </c>
+      <c r="G4" t="n">
+        <v>15601</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -530,6 +558,12 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>21971</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -549,6 +583,12 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7508</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -568,6 +608,12 @@
       <c r="E7" t="n">
         <v>5</v>
       </c>
+      <c r="F7" t="n">
+        <v>3498</v>
+      </c>
+      <c r="G7" t="n">
+        <v>21516</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -587,6 +633,12 @@
       <c r="E8" t="n">
         <v>1</v>
       </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>17997</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -606,6 +658,12 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>18127</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -625,6 +683,12 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7802</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -644,6 +708,12 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11030</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -663,6 +733,12 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12596</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -682,6 +758,12 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>11946</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -701,6 +783,12 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>17334</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -720,6 +808,12 @@
       <c r="E15" t="n">
         <v>0</v>
       </c>
+      <c r="F15" t="n">
+        <v>534</v>
+      </c>
+      <c r="G15" t="n">
+        <v>23341</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -739,6 +833,12 @@
       <c r="E16" t="n">
         <v>0</v>
       </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>15332</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -758,6 +858,12 @@
       <c r="E17" t="n">
         <v>5</v>
       </c>
+      <c r="F17" t="n">
+        <v>3287</v>
+      </c>
+      <c r="G17" t="n">
+        <v>19433</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -777,6 +883,12 @@
       <c r="E18" t="n">
         <v>0</v>
       </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>17702</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -796,6 +908,12 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4303</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -815,6 +933,12 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>22651</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -834,6 +958,12 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6824</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -853,6 +983,12 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>23782</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -872,6 +1008,12 @@
       <c r="E23" t="n">
         <v>0</v>
       </c>
+      <c r="F23" t="n">
+        <v>928</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22642</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -891,6 +1033,12 @@
       <c r="E24" t="n">
         <v>0</v>
       </c>
+      <c r="F24" t="n">
+        <v>1132</v>
+      </c>
+      <c r="G24" t="n">
+        <v>23393</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -910,6 +1058,12 @@
       <c r="E25" t="n">
         <v>2</v>
       </c>
+      <c r="F25" t="n">
+        <v>5827</v>
+      </c>
+      <c r="G25" t="n">
+        <v>35395</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -929,6 +1083,12 @@
       <c r="E26" t="n">
         <v>0</v>
       </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>12667</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -948,6 +1108,12 @@
       <c r="E27" t="n">
         <v>0</v>
       </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9527</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -967,6 +1133,12 @@
       <c r="E28" t="n">
         <v>0</v>
       </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5595</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -986,6 +1158,12 @@
       <c r="E29" t="n">
         <v>0</v>
       </c>
+      <c r="F29" t="n">
+        <v>1127</v>
+      </c>
+      <c r="G29" t="n">
+        <v>13226</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1005,6 +1183,12 @@
       <c r="E30" t="n">
         <v>0</v>
       </c>
+      <c r="F30" t="n">
+        <v>1715</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1024,6 +1208,12 @@
       <c r="E31" t="n">
         <v>0</v>
       </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>24732</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1043,6 +1233,12 @@
       <c r="E32" t="n">
         <v>2</v>
       </c>
+      <c r="F32" t="n">
+        <v>3857</v>
+      </c>
+      <c r="G32" t="n">
+        <v>15641</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1062,6 +1258,12 @@
       <c r="E33" t="n">
         <v>0</v>
       </c>
+      <c r="F33" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G33" t="n">
+        <v>17339</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1081,6 +1283,12 @@
       <c r="E34" t="n">
         <v>0</v>
       </c>
+      <c r="F34" t="n">
+        <v>2575</v>
+      </c>
+      <c r="G34" t="n">
+        <v>13315</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1100,6 +1308,12 @@
       <c r="E35" t="n">
         <v>0</v>
       </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5571</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1119,6 +1333,12 @@
       <c r="E36" t="n">
         <v>0</v>
       </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>12377</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1138,6 +1358,12 @@
       <c r="E37" t="n">
         <v>0</v>
       </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>13131</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1157,6 +1383,12 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>26812</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1176,6 +1408,12 @@
       <c r="E39" t="n">
         <v>0</v>
       </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3194</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1195,6 +1433,12 @@
       <c r="E40" t="n">
         <v>8</v>
       </c>
+      <c r="F40" t="n">
+        <v>5973</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34821</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1214,6 +1458,12 @@
       <c r="E41" t="n">
         <v>0</v>
       </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>13668</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1233,6 +1483,12 @@
       <c r="E42" t="n">
         <v>0</v>
       </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5260</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1252,6 +1508,12 @@
       <c r="E43" t="n">
         <v>1</v>
       </c>
+      <c r="F43" t="n">
+        <v>3467</v>
+      </c>
+      <c r="G43" t="n">
+        <v>15317</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1271,6 +1533,12 @@
       <c r="E44" t="n">
         <v>0</v>
       </c>
+      <c r="F44" t="n">
+        <v>111</v>
+      </c>
+      <c r="G44" t="n">
+        <v>9792</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1290,6 +1558,12 @@
       <c r="E45" t="n">
         <v>0</v>
       </c>
+      <c r="F45" t="n">
+        <v>6524</v>
+      </c>
+      <c r="G45" t="n">
+        <v>6516</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1309,6 +1583,12 @@
       <c r="E46" t="n">
         <v>0</v>
       </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1938</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1328,6 +1608,12 @@
       <c r="E47" t="n">
         <v>4</v>
       </c>
+      <c r="F47" t="n">
+        <v>3069</v>
+      </c>
+      <c r="G47" t="n">
+        <v>21283</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1347,6 +1633,12 @@
       <c r="E48" t="n">
         <v>0</v>
       </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5838</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1366,6 +1658,12 @@
       <c r="E49" t="n">
         <v>0</v>
       </c>
+      <c r="F49" t="n">
+        <v>1332</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7774</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1385,6 +1683,12 @@
       <c r="E50" t="n">
         <v>0</v>
       </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>9431</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1404,6 +1708,12 @@
       <c r="E51" t="n">
         <v>0</v>
       </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>24512</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1423,6 +1733,12 @@
       <c r="E52" t="n">
         <v>0</v>
       </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>19209</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1442,6 +1758,12 @@
       <c r="E53" t="n">
         <v>0</v>
       </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8509</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1461,6 +1783,12 @@
       <c r="E54" t="n">
         <v>5</v>
       </c>
+      <c r="F54" t="n">
+        <v>2919</v>
+      </c>
+      <c r="G54" t="n">
+        <v>20235</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1480,6 +1808,12 @@
       <c r="E55" t="n">
         <v>0</v>
       </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>13782</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1499,6 +1833,12 @@
       <c r="E56" t="n">
         <v>0</v>
       </c>
+      <c r="F56" t="n">
+        <v>2653</v>
+      </c>
+      <c r="G56" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1518,6 +1858,12 @@
       <c r="E57" t="n">
         <v>0</v>
       </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1847</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1537,6 +1883,12 @@
       <c r="E58" t="n">
         <v>0</v>
       </c>
+      <c r="F58" t="n">
+        <v>1769</v>
+      </c>
+      <c r="G58" t="n">
+        <v>20275</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1556,6 +1908,12 @@
       <c r="E59" t="n">
         <v>10</v>
       </c>
+      <c r="F59" t="n">
+        <v>1459</v>
+      </c>
+      <c r="G59" t="n">
+        <v>26207</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1575,6 +1933,12 @@
       <c r="E60" t="n">
         <v>1</v>
       </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>24056</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1594,6 +1958,12 @@
       <c r="E61" t="n">
         <v>0</v>
       </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>7140</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1613,6 +1983,12 @@
       <c r="E62" t="n">
         <v>0</v>
       </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>14656</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1632,6 +2008,12 @@
       <c r="E63" t="n">
         <v>0</v>
       </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>10739</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1651,6 +2033,12 @@
       <c r="E64" t="n">
         <v>0</v>
       </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>19778</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1670,6 +2058,12 @@
       <c r="E65" t="n">
         <v>6</v>
       </c>
+      <c r="F65" t="n">
+        <v>5495</v>
+      </c>
+      <c r="G65" t="n">
+        <v>18582</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1689,6 +2083,12 @@
       <c r="E66" t="n">
         <v>0</v>
       </c>
+      <c r="F66" t="n">
+        <v>5278</v>
+      </c>
+      <c r="G66" t="n">
+        <v>9695</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1708,6 +2108,12 @@
       <c r="E67" t="n">
         <v>0</v>
       </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4171</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1727,6 +2133,12 @@
       <c r="E68" t="n">
         <v>0</v>
       </c>
+      <c r="F68" t="n">
+        <v>1577</v>
+      </c>
+      <c r="G68" t="n">
+        <v>18106</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1746,6 +2158,12 @@
       <c r="E69" t="n">
         <v>0</v>
       </c>
+      <c r="F69" t="n">
+        <v>236</v>
+      </c>
+      <c r="G69" t="n">
+        <v>17774</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1765,6 +2183,12 @@
       <c r="E70" t="n">
         <v>0</v>
       </c>
+      <c r="F70" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G70" t="n">
+        <v>21237</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1784,6 +2208,12 @@
       <c r="E71" t="n">
         <v>0</v>
       </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>15776</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1803,6 +2233,12 @@
       <c r="E72" t="n">
         <v>0</v>
       </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>11300</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1822,6 +2258,12 @@
       <c r="E73" t="n">
         <v>0</v>
       </c>
+      <c r="F73" t="n">
+        <v>4399</v>
+      </c>
+      <c r="G73" t="n">
+        <v>9915</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1841,6 +2283,12 @@
       <c r="E74" t="n">
         <v>0</v>
       </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>9142</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1860,6 +2308,12 @@
       <c r="E75" t="n">
         <v>0</v>
       </c>
+      <c r="F75" t="n">
+        <v>257</v>
+      </c>
+      <c r="G75" t="n">
+        <v>7246</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1879,6 +2333,12 @@
       <c r="E76" t="n">
         <v>0</v>
       </c>
+      <c r="F76" t="n">
+        <v>1981</v>
+      </c>
+      <c r="G76" t="n">
+        <v>20322</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1898,6 +2358,12 @@
       <c r="E77" t="n">
         <v>3</v>
       </c>
+      <c r="F77" t="n">
+        <v>1959</v>
+      </c>
+      <c r="G77" t="n">
+        <v>39369</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1917,6 +2383,12 @@
       <c r="E78" t="n">
         <v>0</v>
       </c>
+      <c r="F78" t="n">
+        <v>1379</v>
+      </c>
+      <c r="G78" t="n">
+        <v>29377</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1936,6 +2408,12 @@
       <c r="E79" t="n">
         <v>0</v>
       </c>
+      <c r="F79" t="n">
+        <v>930</v>
+      </c>
+      <c r="G79" t="n">
+        <v>36086</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1955,6 +2433,12 @@
       <c r="E80" t="n">
         <v>0</v>
       </c>
+      <c r="F80" t="n">
+        <v>1708</v>
+      </c>
+      <c r="G80" t="n">
+        <v>12838</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1974,6 +2458,12 @@
       <c r="E81" t="n">
         <v>0</v>
       </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>11950</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1993,6 +2483,12 @@
       <c r="E82" t="n">
         <v>1</v>
       </c>
+      <c r="F82" t="n">
+        <v>3078</v>
+      </c>
+      <c r="G82" t="n">
+        <v>12142</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2012,6 +2508,12 @@
       <c r="E83" t="n">
         <v>6</v>
       </c>
+      <c r="F83" t="n">
+        <v>4717</v>
+      </c>
+      <c r="G83" t="n">
+        <v>37941</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2031,6 +2533,12 @@
       <c r="E84" t="n">
         <v>0</v>
       </c>
+      <c r="F84" t="n">
+        <v>551</v>
+      </c>
+      <c r="G84" t="n">
+        <v>41298</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2050,6 +2558,12 @@
       <c r="E85" t="n">
         <v>0</v>
       </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3714</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2069,6 +2583,12 @@
       <c r="E86" t="n">
         <v>4</v>
       </c>
+      <c r="F86" t="n">
+        <v>8226</v>
+      </c>
+      <c r="G86" t="n">
+        <v>64812</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2088,6 +2608,12 @@
       <c r="E87" t="n">
         <v>0</v>
       </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>18483</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2107,6 +2633,12 @@
       <c r="E88" t="n">
         <v>0</v>
       </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>10426</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2126,6 +2658,12 @@
       <c r="E89" t="n">
         <v>1</v>
       </c>
+      <c r="F89" t="n">
+        <v>2766</v>
+      </c>
+      <c r="G89" t="n">
+        <v>14660</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2145,6 +2683,12 @@
       <c r="E90" t="n">
         <v>0</v>
       </c>
+      <c r="F90" t="n">
+        <v>4014</v>
+      </c>
+      <c r="G90" t="n">
+        <v>33765</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2164,6 +2708,12 @@
       <c r="E91" t="n">
         <v>0</v>
       </c>
+      <c r="F91" t="n">
+        <v>6252</v>
+      </c>
+      <c r="G91" t="n">
+        <v>20267</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2183,6 +2733,12 @@
       <c r="E92" t="n">
         <v>0</v>
       </c>
+      <c r="F92" t="n">
+        <v>1762</v>
+      </c>
+      <c r="G92" t="n">
+        <v>6850</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2202,6 +2758,12 @@
       <c r="E93" t="n">
         <v>0</v>
       </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>16619</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2221,6 +2783,12 @@
       <c r="E94" t="n">
         <v>0</v>
       </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>4667</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2240,6 +2808,12 @@
       <c r="E95" t="n">
         <v>0</v>
       </c>
+      <c r="F95" t="n">
+        <v>3061</v>
+      </c>
+      <c r="G95" t="n">
+        <v>22126</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2259,6 +2833,12 @@
       <c r="E96" t="n">
         <v>0</v>
       </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>6515</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2278,6 +2858,12 @@
       <c r="E97" t="n">
         <v>0</v>
       </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>15891</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2297,6 +2883,12 @@
       <c r="E98" t="n">
         <v>0</v>
       </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>14669</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2316,6 +2908,12 @@
       <c r="E99" t="n">
         <v>1</v>
       </c>
+      <c r="F99" t="n">
+        <v>2194</v>
+      </c>
+      <c r="G99" t="n">
+        <v>21812</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2335,6 +2933,12 @@
       <c r="E100" t="n">
         <v>0</v>
       </c>
+      <c r="F100" t="n">
+        <v>2880</v>
+      </c>
+      <c r="G100" t="n">
+        <v>13421</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2354,6 +2958,12 @@
       <c r="E101" t="n">
         <v>0</v>
       </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>10642</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2373,6 +2983,12 @@
       <c r="E102" t="n">
         <v>0</v>
       </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>17733</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2392,6 +3008,12 @@
       <c r="E103" t="n">
         <v>4</v>
       </c>
+      <c r="F103" t="n">
+        <v>6024</v>
+      </c>
+      <c r="G103" t="n">
+        <v>24674</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2411,6 +3033,12 @@
       <c r="E104" t="n">
         <v>0</v>
       </c>
+      <c r="F104" t="n">
+        <v>2970</v>
+      </c>
+      <c r="G104" t="n">
+        <v>7238</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2430,6 +3058,12 @@
       <c r="E105" t="n">
         <v>0</v>
       </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>9776</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2449,6 +3083,12 @@
       <c r="E106" t="n">
         <v>0</v>
       </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3521</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2468,6 +3108,12 @@
       <c r="E107" t="n">
         <v>0</v>
       </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>3370</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2487,6 +3133,12 @@
       <c r="E108" t="n">
         <v>0</v>
       </c>
+      <c r="F108" t="n">
+        <v>16039</v>
+      </c>
+      <c r="G108" t="n">
+        <v>61952</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2506,6 +3158,12 @@
       <c r="E109" t="n">
         <v>0</v>
       </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>22743</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2525,6 +3183,12 @@
       <c r="E110" t="n">
         <v>0</v>
       </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>9235</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2544,6 +3208,12 @@
       <c r="E111" t="n">
         <v>0</v>
       </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>7755</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2563,6 +3233,12 @@
       <c r="E112" t="n">
         <v>0</v>
       </c>
+      <c r="F112" t="n">
+        <v>1748</v>
+      </c>
+      <c r="G112" t="n">
+        <v>28084</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2582,6 +3258,12 @@
       <c r="E113" t="n">
         <v>0</v>
       </c>
+      <c r="F113" t="n">
+        <v>5430</v>
+      </c>
+      <c r="G113" t="n">
+        <v>15486</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2601,6 +3283,12 @@
       <c r="E114" t="n">
         <v>4</v>
       </c>
+      <c r="F114" t="n">
+        <v>9012</v>
+      </c>
+      <c r="G114" t="n">
+        <v>14190</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2620,6 +3308,12 @@
       <c r="E115" t="n">
         <v>0</v>
       </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>28619</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2639,6 +3333,12 @@
       <c r="E116" t="n">
         <v>0</v>
       </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>24872</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2658,6 +3358,12 @@
       <c r="E117" t="n">
         <v>1</v>
       </c>
+      <c r="F117" t="n">
+        <v>3757</v>
+      </c>
+      <c r="G117" t="n">
+        <v>25699</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2677,6 +3383,12 @@
       <c r="E118" t="n">
         <v>0</v>
       </c>
+      <c r="F118" t="n">
+        <v>2538</v>
+      </c>
+      <c r="G118" t="n">
+        <v>32560</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2696,6 +3408,12 @@
       <c r="E119" t="n">
         <v>0</v>
       </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>6837</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2715,6 +3433,12 @@
       <c r="E120" t="n">
         <v>0</v>
       </c>
+      <c r="F120" t="n">
+        <v>1171</v>
+      </c>
+      <c r="G120" t="n">
+        <v>27018</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2734,6 +3458,12 @@
       <c r="E121" t="n">
         <v>0</v>
       </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4319</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2753,6 +3483,12 @@
       <c r="E122" t="n">
         <v>1</v>
       </c>
+      <c r="F122" t="n">
+        <v>4377</v>
+      </c>
+      <c r="G122" t="n">
+        <v>6585</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2772,6 +3508,12 @@
       <c r="E123" t="n">
         <v>0</v>
       </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>13128</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2791,6 +3533,12 @@
       <c r="E124" t="n">
         <v>0</v>
       </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>14112</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2810,6 +3558,12 @@
       <c r="E125" t="n">
         <v>0</v>
       </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>11772</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2829,6 +3583,12 @@
       <c r="E126" t="n">
         <v>0</v>
       </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>5502</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2848,6 +3608,12 @@
       <c r="E127" t="n">
         <v>0</v>
       </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>6757</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2867,6 +3633,12 @@
       <c r="E128" t="n">
         <v>0</v>
       </c>
+      <c r="F128" t="n">
+        <v>849</v>
+      </c>
+      <c r="G128" t="n">
+        <v>24112</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2886,6 +3658,12 @@
       <c r="E129" t="n">
         <v>2</v>
       </c>
+      <c r="F129" t="n">
+        <v>3940</v>
+      </c>
+      <c r="G129" t="n">
+        <v>42462</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2905,6 +3683,12 @@
       <c r="E130" t="n">
         <v>1</v>
       </c>
+      <c r="F130" t="n">
+        <v>3254</v>
+      </c>
+      <c r="G130" t="n">
+        <v>12401</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2924,6 +3708,12 @@
       <c r="E131" t="n">
         <v>0</v>
       </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>14901</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2943,6 +3733,12 @@
       <c r="E132" t="n">
         <v>0</v>
       </c>
+      <c r="F132" t="n">
+        <v>3738</v>
+      </c>
+      <c r="G132" t="n">
+        <v>26294</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2962,6 +3758,12 @@
       <c r="E133" t="n">
         <v>0</v>
       </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>11854</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2981,6 +3783,12 @@
       <c r="E134" t="n">
         <v>0</v>
       </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>11350</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3000,6 +3808,12 @@
       <c r="E135" t="n">
         <v>0</v>
       </c>
+      <c r="F135" t="n">
+        <v>561</v>
+      </c>
+      <c r="G135" t="n">
+        <v>20717</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3019,6 +3833,12 @@
       <c r="E136" t="n">
         <v>0</v>
       </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>13494</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3038,6 +3858,12 @@
       <c r="E137" t="n">
         <v>0</v>
       </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>18227</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3057,6 +3883,12 @@
       <c r="E138" t="n">
         <v>0</v>
       </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>19813</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3076,6 +3908,12 @@
       <c r="E139" t="n">
         <v>0</v>
       </c>
+      <c r="F139" t="n">
+        <v>967</v>
+      </c>
+      <c r="G139" t="n">
+        <v>20769</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3095,6 +3933,12 @@
       <c r="E140" t="n">
         <v>9</v>
       </c>
+      <c r="F140" t="n">
+        <v>2444</v>
+      </c>
+      <c r="G140" t="n">
+        <v>22590</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3114,6 +3958,12 @@
       <c r="E141" t="n">
         <v>0</v>
       </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>19663</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3133,6 +3983,12 @@
       <c r="E142" t="n">
         <v>0</v>
       </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>13484</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3152,6 +4008,12 @@
       <c r="E143" t="n">
         <v>0</v>
       </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>11096</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3171,6 +4033,12 @@
       <c r="E144" t="n">
         <v>0</v>
       </c>
+      <c r="F144" t="n">
+        <v>1099</v>
+      </c>
+      <c r="G144" t="n">
+        <v>28340</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3189,6 +4057,12 @@
       </c>
       <c r="E145" t="n">
         <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>9990</v>
       </c>
     </row>
   </sheetData>
